--- a/research/traditional_assets/database/data/australia/australia_oil_gas_distribution.xlsx
+++ b/research/traditional_assets/database/data/australia/australia_oil_gas_distribution.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="K2">
-        <v>-2.32</v>
+        <v>-4.66</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -612,70 +612,70 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>4.92</v>
+        <v>8</v>
       </c>
       <c r="V2">
-        <v>0.1131034482758621</v>
+        <v>0.4678362573099415</v>
       </c>
       <c r="W2">
-        <v>-0.3642072213500784</v>
+        <v>-0.5070729053318825</v>
       </c>
       <c r="X2">
-        <v>0.04492988799134406</v>
+        <v>0.07695937938240954</v>
       </c>
       <c r="Y2">
-        <v>-0.4091371093414225</v>
+        <v>-0.584032284714292</v>
       </c>
       <c r="Z2">
         <v>0</v>
       </c>
       <c r="AA2">
-        <v>-0.5817267049226225</v>
+        <v>-1.14855090851701</v>
       </c>
       <c r="AB2">
-        <v>0.0449213855360538</v>
+        <v>0.07695344856225528</v>
       </c>
       <c r="AC2">
-        <v>-0.6266480904586763</v>
+        <v>-1.225504357079265</v>
       </c>
       <c r="AD2">
         <v>0</v>
       </c>
       <c r="AE2">
-        <v>0.01459195160212005</v>
+        <v>0.002833396297695505</v>
       </c>
       <c r="AF2">
-        <v>0.01459195160212005</v>
+        <v>0.002833396297695505</v>
       </c>
       <c r="AG2">
-        <v>-4.90540804839788</v>
+        <v>-7.997166603702304</v>
       </c>
       <c r="AH2">
-        <v>0.0003353346762012507</v>
+        <v>0.0001656682394104861</v>
       </c>
       <c r="AI2">
-        <v>0.00158529043751692</v>
+        <v>0.0002484817763465228</v>
       </c>
       <c r="AJ2">
-        <v>-0.1271009175210168</v>
+        <v>-0.8785359739699191</v>
       </c>
       <c r="AK2">
-        <v>-1.144895034068208</v>
+        <v>-2.350149323326634</v>
       </c>
       <c r="AL2">
         <v>0</v>
       </c>
       <c r="AM2">
-        <v>-0.001</v>
+        <v>-0.016</v>
       </c>
       <c r="AN2">
         <v>-0</v>
       </c>
       <c r="AP2">
-        <v>2.30842731689312</v>
+        <v>1.732113191185251</v>
       </c>
       <c r="AQ2">
-        <v>2490</v>
+        <v>306.875</v>
       </c>
     </row>
     <row r="3">
@@ -686,7 +686,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Global Energy Ventures Ltd. (ASX:GEV)</t>
+          <t>Provaris Energy Ltd (ASX:PV1)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -695,7 +695,7 @@
         </is>
       </c>
       <c r="K3">
-        <v>-2.32</v>
+        <v>-4.66</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -719,70 +719,70 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>4.92</v>
+        <v>8</v>
       </c>
       <c r="V3">
-        <v>0.1131034482758621</v>
+        <v>0.4678362573099415</v>
       </c>
       <c r="W3">
-        <v>-0.3642072213500784</v>
+        <v>-0.5070729053318825</v>
       </c>
       <c r="X3">
-        <v>0.04492988799134406</v>
+        <v>0.07695937938240954</v>
       </c>
       <c r="Y3">
-        <v>-0.4091371093414225</v>
+        <v>-0.584032284714292</v>
       </c>
       <c r="Z3">
         <v>0</v>
       </c>
       <c r="AA3">
-        <v>-0.5817267049226225</v>
+        <v>-1.14855090851701</v>
       </c>
       <c r="AB3">
-        <v>0.0449213855360538</v>
+        <v>0.07695344856225528</v>
       </c>
       <c r="AC3">
-        <v>-0.6266480904586763</v>
+        <v>-1.225504357079265</v>
       </c>
       <c r="AD3">
         <v>0</v>
       </c>
       <c r="AE3">
-        <v>0.01459195160212005</v>
+        <v>0.002833396297695505</v>
       </c>
       <c r="AF3">
-        <v>0.01459195160212005</v>
+        <v>0.002833396297695505</v>
       </c>
       <c r="AG3">
-        <v>-4.90540804839788</v>
+        <v>-7.997166603702304</v>
       </c>
       <c r="AH3">
-        <v>0.0003353346762012507</v>
+        <v>0.0001656682394104861</v>
       </c>
       <c r="AI3">
-        <v>0.00158529043751692</v>
+        <v>0.0002484817763465228</v>
       </c>
       <c r="AJ3">
-        <v>-0.1271009175210168</v>
+        <v>-0.8785359739699191</v>
       </c>
       <c r="AK3">
-        <v>-1.144895034068208</v>
+        <v>-2.350149323326634</v>
       </c>
       <c r="AL3">
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>-0.001</v>
+        <v>-0.016</v>
       </c>
       <c r="AN3">
         <v>-0</v>
       </c>
       <c r="AP3">
-        <v>2.30842731689312</v>
+        <v>1.732113191185251</v>
       </c>
       <c r="AQ3">
-        <v>2490</v>
+        <v>306.875</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/australia/australia_oil_gas_distribution.xlsx
+++ b/research/traditional_assets/database/data/australia/australia_oil_gas_distribution.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="K2">
-        <v>-4.66</v>
+        <v>-8.26</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -612,70 +612,70 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>8</v>
+        <v>3.37</v>
       </c>
       <c r="V2">
-        <v>0.4678362573099415</v>
+        <v>0.1635922330097087</v>
       </c>
       <c r="W2">
-        <v>-0.5070729053318825</v>
+        <v>-0.7245614035087719</v>
       </c>
       <c r="X2">
-        <v>0.07695937938240954</v>
+        <v>0.06485375209446337</v>
       </c>
       <c r="Y2">
-        <v>-0.584032284714292</v>
+        <v>-0.7894151556032352</v>
       </c>
       <c r="Z2">
         <v>0</v>
       </c>
       <c r="AA2">
-        <v>-1.14855090851701</v>
+        <v>-1.519474533870287</v>
       </c>
       <c r="AB2">
-        <v>0.07695344856225528</v>
+        <v>0.0648348363585006</v>
       </c>
       <c r="AC2">
-        <v>-1.225504357079265</v>
+        <v>-1.584309370228788</v>
       </c>
       <c r="AD2">
         <v>0</v>
       </c>
       <c r="AE2">
-        <v>0.002833396297695505</v>
+        <v>0.01423792908372282</v>
       </c>
       <c r="AF2">
-        <v>0.002833396297695505</v>
+        <v>0.01423792908372282</v>
       </c>
       <c r="AG2">
-        <v>-7.997166603702304</v>
+        <v>-3.355762070916277</v>
       </c>
       <c r="AH2">
-        <v>0.0001656682394104861</v>
+        <v>0.000690684231583218</v>
       </c>
       <c r="AI2">
-        <v>0.0002484817763465228</v>
+        <v>0.004919405188028325</v>
       </c>
       <c r="AJ2">
-        <v>-0.8785359739699191</v>
+        <v>-0.1946019351343169</v>
       </c>
       <c r="AK2">
-        <v>-2.350149323326634</v>
+        <v>7.053445989196584</v>
       </c>
       <c r="AL2">
         <v>0</v>
       </c>
       <c r="AM2">
-        <v>-0.016</v>
+        <v>-0.103</v>
       </c>
       <c r="AN2">
         <v>-0</v>
       </c>
       <c r="AP2">
-        <v>1.732113191185251</v>
+        <v>0.6651659208951987</v>
       </c>
       <c r="AQ2">
-        <v>306.875</v>
+        <v>50.48543689320389</v>
       </c>
     </row>
     <row r="3">
@@ -695,7 +695,7 @@
         </is>
       </c>
       <c r="K3">
-        <v>-4.66</v>
+        <v>-8.26</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -719,70 +719,70 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>8</v>
+        <v>3.37</v>
       </c>
       <c r="V3">
-        <v>0.4678362573099415</v>
+        <v>0.1635922330097087</v>
       </c>
       <c r="W3">
-        <v>-0.5070729053318825</v>
+        <v>-0.7245614035087719</v>
       </c>
       <c r="X3">
-        <v>0.07695937938240954</v>
+        <v>0.06485375209446337</v>
       </c>
       <c r="Y3">
-        <v>-0.584032284714292</v>
+        <v>-0.7894151556032352</v>
       </c>
       <c r="Z3">
         <v>0</v>
       </c>
       <c r="AA3">
-        <v>-1.14855090851701</v>
+        <v>-1.519474533870287</v>
       </c>
       <c r="AB3">
-        <v>0.07695344856225528</v>
+        <v>0.0648348363585006</v>
       </c>
       <c r="AC3">
-        <v>-1.225504357079265</v>
+        <v>-1.584309370228788</v>
       </c>
       <c r="AD3">
         <v>0</v>
       </c>
       <c r="AE3">
-        <v>0.002833396297695505</v>
+        <v>0.01423792908372282</v>
       </c>
       <c r="AF3">
-        <v>0.002833396297695505</v>
+        <v>0.01423792908372282</v>
       </c>
       <c r="AG3">
-        <v>-7.997166603702304</v>
+        <v>-3.355762070916277</v>
       </c>
       <c r="AH3">
-        <v>0.0001656682394104861</v>
+        <v>0.000690684231583218</v>
       </c>
       <c r="AI3">
-        <v>0.0002484817763465228</v>
+        <v>0.004919405188028325</v>
       </c>
       <c r="AJ3">
-        <v>-0.8785359739699191</v>
+        <v>-0.1946019351343169</v>
       </c>
       <c r="AK3">
-        <v>-2.350149323326634</v>
+        <v>7.053445989196584</v>
       </c>
       <c r="AL3">
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>-0.016</v>
+        <v>-0.103</v>
       </c>
       <c r="AN3">
         <v>-0</v>
       </c>
       <c r="AP3">
-        <v>1.732113191185251</v>
+        <v>0.6651659208951987</v>
       </c>
       <c r="AQ3">
-        <v>306.875</v>
+        <v>50.48543689320389</v>
       </c>
     </row>
   </sheetData>
